--- a/AI_AuditLog_Example.xlsx
+++ b/AI_AuditLog_Example.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FPT\SU2026\SWR302\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FPT\SU2026\SWR302\SWR302_Exercise\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{281229CA-329E-42A8-BEFC-AD37373585E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A778CF4C-C04F-42D0-844F-A239D8BD6F0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6400" yWindow="4110" windowWidth="19200" windowHeight="11170" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Metadata &amp; Summary" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="132">
   <si>
     <t>AI AUDIT LOG - METADATA &amp; SUMMARY</t>
   </si>
@@ -60,15 +60,9 @@
     <t>Total Prompts Used (all AI tools):</t>
   </si>
   <si>
-    <t>[e.g., ~150]</t>
-  </si>
-  <si>
     <t>Core Prompts Logged:</t>
   </si>
   <si>
-    <t>[e.g., 18]</t>
-  </si>
-  <si>
     <t>Selection Ratio:</t>
   </si>
   <si>
@@ -78,9 +72,6 @@
     <t>Hallucination Detected:</t>
   </si>
   <si>
-    <t>[Count]</t>
-  </si>
-  <si>
     <t>AI TOOLS USED</t>
   </si>
   <si>
@@ -96,42 +87,9 @@
     <t>Main Value</t>
   </si>
   <si>
-    <t>ChatGPT</t>
-  </si>
-  <si>
-    <t>Code generation, debugging</t>
-  </si>
-  <si>
     <t>High</t>
   </si>
   <si>
-    <t>Rapid prototyping</t>
-  </si>
-  <si>
-    <t>Claude</t>
-  </si>
-  <si>
-    <t>Requirement analysis, design review</t>
-  </si>
-  <si>
-    <t>Medium</t>
-  </si>
-  <si>
-    <t>Deep reflection</t>
-  </si>
-  <si>
-    <t>GitHub Copilot</t>
-  </si>
-  <si>
-    <t>Auto-completion</t>
-  </si>
-  <si>
-    <t>Speed up coding</t>
-  </si>
-  <si>
-    <t>[Add more...]</t>
-  </si>
-  <si>
     <t>CORE PROMPTS DISTRIBUTION BY DTC COMPONENT</t>
   </si>
   <si>
@@ -195,75 +153,15 @@
     <t>DECISION</t>
   </si>
   <si>
-    <t>Cần chia nhỏ requirement</t>
-  </si>
-  <si>
-    <t>Break down student management into modules</t>
-  </si>
-  <si>
-    <t>AI suggested 10 modules: User, Student, Course, Grade, Attendance, Report, Export, Import, Settings, Dashboard</t>
-  </si>
-  <si>
-    <t>Critical Thinking: 10 modules quá nhiều cho project 300 LOC.
-Contextualization: Project scope nhỏ, chỉ cần core functions.
-Creative Synthesis: Tôi gộp thành 5 modules: Student, Grade, File I/O, Validation, UI.
-Decision: Chọn 5 modules vì đủ để implement requirements mà không phức tạp.</t>
-  </si>
-  <si>
-    <t>Screenshot comparison 10 vs 5</t>
-  </si>
-  <si>
     <t>002</t>
   </si>
   <si>
     <t>PROBLEM-SOLVING</t>
   </si>
   <si>
-    <t>Search by name quá chậm với 10K records</t>
-  </si>
-  <si>
-    <t>How to optimize search for player name in 10,000 records?</t>
-  </si>
-  <si>
-    <t>AI suggested Binary Search with O(log n) complexity</t>
-  </si>
-  <si>
-    <t>Critical Thinking: Binary Search cần sort trước → O(n log n). Với partial match không phù hợp.
-Contextualization: Requirements yêu cầu partial name search.
-Creative Synthesis: Test 3 approaches: Binary Search, Linear Search, HashMap. HashMap fastest (2ms).
-Decision: Chọn HashMap trade-off memory cho speed.</t>
-  </si>
-  <si>
-    <t>Code snippet + timing comparison</t>
-  </si>
-  <si>
     <t>003</t>
   </si>
   <si>
-    <t>VERIFICATION</t>
-  </si>
-  <si>
-    <t>Literature Review</t>
-  </si>
-  <si>
-    <t>Cần verify paper AI cite</t>
-  </si>
-  <si>
-    <t>Is the paper 'Smith et al. 2023 on IoT anomaly detection' a real publication?</t>
-  </si>
-  <si>
-    <t>AI confirmed it exists and provided summary</t>
-  </si>
-  <si>
-    <t>Critical Thinking: HALLUCINATION DETECTED! Search Google Scholar → paper NOT FOUND.
-Contextualization: AI fabricated paper to answer my question.
-Creative Synthesis: Found real paper 'Jones et al. 2022' with similar topic.
-Decision: Replace with verified paper from Google Scholar.</t>
-  </si>
-  <si>
-    <t>Google Scholar screenshot</t>
-  </si>
-  <si>
     <t>HALLUCINATION DETECTION LOG (BẮT BUỘC)</t>
   </si>
   <si>
@@ -291,18 +189,6 @@
     <t>Fabrication</t>
   </si>
   <si>
-    <t>Paper 'Smith et al. 2023' exists</t>
-  </si>
-  <si>
-    <t>Paper NOT FOUND on Google Scholar</t>
-  </si>
-  <si>
-    <t>Searched Google Scholar, ResearchGate</t>
-  </si>
-  <si>
-    <t>Used real paper 'Jones et al. 2022'</t>
-  </si>
-  <si>
     <t>HALLUCINATION TYPES REFERENCE:</t>
   </si>
   <si>
@@ -384,9 +270,6 @@
     <t>Prompt này ảnh hưởng đến quyết định quan trọng trong project?</t>
   </si>
   <si>
-    <t>☐</t>
-  </si>
-  <si>
     <t>2</t>
   </si>
   <si>
@@ -463,6 +346,92 @@
   </si>
   <si>
     <t>SWR302</t>
+  </si>
+  <si>
+    <t>Bài tập cá nhân Chương 16 &amp; 17</t>
+  </si>
+  <si>
+    <t>Gemini</t>
+  </si>
+  <si>
+    <t>Requirement analysis, Test case generation</t>
+  </si>
+  <si>
+    <t>Deep reflection, rapid prototyping cho bộ khung giải bài tập.</t>
+  </si>
+  <si>
+    <t>Gặp khó khăn trong việc phân biệt rõ ràng giữa "Must Have" và "Should Have" cho dự án đặt lịch khám bệnh có thời gian bị rút ngắn (từ 8 tuần xuống 5 tuần)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> "Dựa vào slide chương 16, hãy giải thích cách phân biệt 'Must Have' và 'Should Have' trong kỹ thuật MoSCoW. Cho tôi một ví dụ về một tính năng 'Should Have' nhưng khách hàng lại hay nhầm là 'Must Have' trong hệ thống y tế để tôi tự liên hệ làm bài."</t>
+  </si>
+  <si>
+    <t>AI giải thích khái niệm dựa trên định nghĩa "Nếu bỏ requirement này đi, hệ thống có còn hoạt động được cho mục đích chính không?". AI ví dụ tính năng "Gửi SMS nhắc lịch" thường bị khách đòi đưa vào Must Have nhưng thực chất chỉ là Should Have.</t>
+  </si>
+  <si>
+    <t>Critical Thinking: Đánh giá cao ví dụ của AI, rất sát với R03 trong bài tập. Contextualization: Tôi tự áp dụng logic này để phân tích 10 requirements của đề bài. Decision: Quyết định tự xếp R01 (đăng ký bằng SĐT) và R06 (đặt lịch 3 cơ sở) vào Must Have, sau đó tự viết giải thích lý do hạ cấp R06 xuống Should Have khi deadline bị rút còn 5 tuần vì vẫn đảm bảo MVP hoạt động được ở 1 cơ sở.</t>
+  </si>
+  <si>
+    <t>Creative Synthesis: Nhận thấy lời khuyên của AI rất hợp lý với bối cảnh thực tế. Decision: Tôi không yêu cầu AI viết test case mà tự thiết kế một kịch bản đặt lịch thành công trên app nhưng Fail ở bước "nhận tin nhắn SMS qua API". Điều này chứng minh được tôi hiểu rõ sự khác biệt giữa Verification (code chạy đúng) và Validation (trải nghiệm thực tế bị lỗi).</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> AI khuyên nên chọn kịch bản Test Fail (có lỗi phát sinh) vì nó mang tính thực tiễn cao hơn, ví dụ như lỗi tích hợp hệ thống bên thứ 3 thay vì mọi thứ đều hoàn hảo.</t>
+  </si>
+  <si>
+    <t>"Trong kịch bản test case ở Bài 3, phần 'Kết quả thực tế' tôi nên giả định tình huống Test Pass hay Test Fail để thể hiện được tư duy phản biện tốt nhất? Hãy cho tôi 1 lời khuyên."</t>
+  </si>
+  <si>
+    <t>Đang viết Test Case cho Acceptance Criteria của tính năng đặt lịch. Chưa biết nên điền "Kết quả thực tế" (Actual Result) như thế nào để ghi điểm tư duy phản biện với giảng viên.</t>
+  </si>
+  <si>
+    <t>Logic Flaw / Inaccurate Reasoning</t>
+  </si>
+  <si>
+    <t>Khi tôi hỏi cách thay thế tính năng "Should Have" (nhắc lịch tự động), AI gợi ý: "Có thể để lễ tân phòng khám gọi điện thủ công cho từng bệnh nhân để nhắc lịch trước 2 tiếng".</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Phòng khám có thể nhận hàng trăm lịch khám mỗi ngày. Việc bắt lễ tân gọi điện cho tất cả mọi người là bất khả thi về mặt nhân sự và thời gian.</t>
+  </si>
+  <si>
+    <t>Phân tích dựa trên ngữ cảnh (business context) và nguồn lực thực tế của một phòng khám.</t>
+  </si>
+  <si>
+    <t>: Bỏ qua gợi ý của AI. Tự đề xuất giải pháp thay thế là: "Bệnh nhân chủ động xem lại giờ khám trên app, hoặc gửi thông báo (notification) nội bộ trong app thay vì SMS".</t>
+  </si>
+  <si>
+    <t>"Lịch sử chỉnh sửa (Version History) của file Word / Ảnh chụp bản nháp trên giấy cho thấy quá trình tự phân tích, đánh dấu các requirement và tự viết lại phần giải thích Must Have."</t>
+  </si>
+  <si>
+    <t>"Ảnh chụp file nháp ghi chú 2 kịch bản Test Case (Pass và Fail) được so sánh cạnh nhau trước khi quyết định chọn kịch bản Fail đưa vào bài nộp chính thức."</t>
+  </si>
+  <si>
+    <t>x</t>
+  </si>
+  <si>
+    <t>Ảnh hưởng trực tiếp đến việc định hình lại scope dự án (hạ cấp R06) để đảm bảo ra mắt MVP đúng hạn trong 5 tuần, và quyết định chọn kịch bản Test Fail để chứng minh sự khác biệt giữa Validation và Verification.</t>
+  </si>
+  <si>
+    <t>Nếu không nhận ra R06 (đặt lịch 3 cơ sở) có thể hạ xuống Should Have, team phát triển sẽ phải thiết kế database và logic điều hướng phức tạp hơn rất nhiều ngay trong phiên bản đầu tiên.</t>
+  </si>
+  <si>
+    <t>Tôi đã tự lập luận bác bỏ gợi ý "lễ tân gọi điện nhắc lịch" của AI vì nó hoàn toàn không khả thi với quy mô tiếp đón của một phòng khám (thiếu tính thực tế).</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Minh chứng sử dụng là lịch sử chỉnh sửa bản nháp (version history) cho phần phân tích MoSCoW và bảng so sánh trực quan giữa 2 kịch bản Test Case (Pass/Fail) trên file nháp.</t>
+  </si>
+  <si>
+    <t>Thể hiện rõ qua việc tôi đã phát hiện ra lỗi logic (Hallucination) của AI trong nghiệp vụ y tế và chủ động thiết kế Test case tập trung vào rủi ro tích hợp bên thứ ba (SMS).</t>
+  </si>
+  <si>
+    <t>"Em chọn cách hạ cấp tính năng R06 (đặt lịch 3 cơ sở) xuống thay vì các tính năng cốt lõi khác vì để thỏa mãn dự án có quỹ thời gian cố định (timebox), ta phải kiểm soát scope creep
+. Việc chỉ chạy 1 cơ sở ở version 1 vẫn giúp hệ thống duy trì được mục đích chính là 'đặt lịch khám'."</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> "Thay vì chọn test case mọi thứ đều đúng, em chọn test case hệ thống chạy đúng tài liệu (Verification pass) nhưng API gửi SMS bị lỗi không gửi được mã cho khách (Validation fail)
+. Cách tiếp cận này minh chứng rõ nhất việc làm đúng yêu cầu kỹ thuật chưa chắc đã đáp ứng được nhu cầu thực tế của use</t>
   </si>
 </sst>
 </file>
@@ -472,7 +441,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -548,6 +517,25 @@
       <sz val="10"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FF2E75B6"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -602,7 +590,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -654,6 +642,21 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -957,7 +960,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
@@ -987,7 +990,7 @@
         <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>137</v>
+        <v>101</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
@@ -995,7 +998,7 @@
         <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>138</v>
+        <v>102</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
@@ -1003,13 +1006,16 @@
         <v>4</v>
       </c>
       <c r="C6" t="s">
-        <v>139</v>
+        <v>103</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>5</v>
       </c>
+      <c r="C7" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="9" spans="1:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A9" s="1" t="s">
@@ -1020,165 +1026,129 @@
       <c r="A10" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C10" t="s">
-        <v>8</v>
+      <c r="C10">
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>10</v>
+        <v>8</v>
+      </c>
+      <c r="C11" s="3">
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C12" s="4" t="e">
+        <v>9</v>
+      </c>
+      <c r="C12" s="4">
         <f>C11/C10</f>
-        <v>#VALUE!</v>
+        <v>1</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>14</v>
+        <v>11</v>
+      </c>
+      <c r="C13" s="3">
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A15" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D16" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B16" s="6" t="s">
+    </row>
+    <row r="17" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A17" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="C17" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="D17" s="7" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A19" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D16" s="6" t="s">
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20" s="6" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" s="7" t="s">
+      <c r="B20" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="C20" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C17" s="7" t="s">
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="B21" s="8">
+        <v>1</v>
+      </c>
+      <c r="C21" s="9" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A18" s="7" t="s">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A22" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="B22" s="8">
+        <v>0</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A23" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A19" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A20" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-    </row>
-    <row r="22" spans="1:4" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A22" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A23" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>35</v>
+      <c r="B23" s="8">
+        <v>1</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" s="7" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="B24" s="8">
         <v>0</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A25" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B25" s="8">
-        <v>0</v>
-      </c>
-      <c r="C25" s="9" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A26" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B26" s="8">
-        <v>0</v>
-      </c>
-      <c r="C26" s="9" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A27" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B27" s="8">
-        <v>0</v>
-      </c>
-      <c r="C27" s="9" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -1191,7 +1161,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1205,7 +1175,7 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="18" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -1217,7 +1187,7 @@
     </row>
     <row r="2" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="20" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="B2" s="19"/>
       <c r="C2" s="19"/>
@@ -1229,107 +1199,91 @@
     </row>
     <row r="3" spans="1:8" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="100" customHeight="1" x14ac:dyDescent="0.35">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="120" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="7" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>53</v>
+        <v>108</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>54</v>
+        <v>109</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>55</v>
+        <v>110</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>56</v>
+        <v>111</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>57</v>
+        <v>121</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="100" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="7" t="s">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>60</v>
+        <v>115</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>61</v>
+        <v>114</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>62</v>
+        <v>113</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>63</v>
+        <v>112</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="100" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>72</v>
-      </c>
+        <v>122</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="80" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="7"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
     </row>
     <row r="7" spans="1:8" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="7"/>
@@ -1521,28 +1475,19 @@
       <c r="G25" s="7"/>
       <c r="H25" s="7"/>
     </row>
-    <row r="26" spans="1:8" ht="80" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="7"/>
-      <c r="B26" s="7"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="7"/>
-      <c r="G26" s="7"/>
-      <c r="H26" s="7"/>
-    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1552,7 +1497,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="22" t="s">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -1562,7 +1507,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="21" t="s">
-        <v>74</v>
+        <v>43</v>
       </c>
       <c r="B2" s="19"/>
       <c r="C2" s="19"/>
@@ -1572,48 +1517,46 @@
     </row>
     <row r="3" spans="1:6" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
-        <v>75</v>
+        <v>44</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>76</v>
+        <v>45</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>77</v>
+        <v>46</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>80</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="7" t="s">
-        <v>65</v>
+      <c r="A4" s="7">
+        <v>1</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>83</v>
+        <v>118</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>84</v>
+        <v>119</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5" s="7" t="s">
-        <v>31</v>
-      </c>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="7"/>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
       <c r="D5" s="7"/>
@@ -1756,91 +1699,75 @@
       <c r="E22" s="7"/>
       <c r="F22" s="7"/>
     </row>
-    <row r="23" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="7"/>
-      <c r="B23" s="7"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="7"/>
-    </row>
-    <row r="24" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="7"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
-    </row>
-    <row r="30" spans="1:6" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A30" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A31" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="B31" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="C31" s="10" t="s">
-        <v>89</v>
+    <row r="28" spans="1:6" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A28" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A29" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="B29" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="C29" s="10" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A30" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A31" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A32" s="7" t="s">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>90</v>
+        <v>61</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>91</v>
+        <v>62</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A33" s="7" t="s">
-        <v>92</v>
+        <v>63</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>93</v>
+        <v>64</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A34" s="7" t="s">
-        <v>95</v>
+        <v>66</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A35" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="B35" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="C35" s="7" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A36" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="B36" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="C36" s="7" t="s">
-        <v>103</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -1864,8 +1791,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" s="18" t="s">
-        <v>104</v>
+      <c r="A1" s="24" t="s">
+        <v>69</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -1873,7 +1800,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="23" t="s">
-        <v>105</v>
+        <v>70</v>
       </c>
       <c r="B2" s="19"/>
       <c r="C2" s="19"/>
@@ -1881,220 +1808,252 @@
     </row>
     <row r="4" spans="1:4" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
-        <v>106</v>
+        <v>71</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="6" t="s">
-        <v>107</v>
+        <v>72</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>108</v>
+        <v>73</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>109</v>
+        <v>74</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="78" x14ac:dyDescent="0.35">
       <c r="A6" s="12" t="s">
-        <v>111</v>
+        <v>76</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>112</v>
-      </c>
-      <c r="C6" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="D6" s="13"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+        <v>77</v>
+      </c>
+      <c r="C6" s="25" t="s">
+        <v>123</v>
+      </c>
+      <c r="D6" s="26" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="78" x14ac:dyDescent="0.35">
       <c r="A7" s="12" t="s">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>115</v>
-      </c>
-      <c r="C7" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="D7" s="13"/>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+        <v>79</v>
+      </c>
+      <c r="C7" s="25" t="s">
+        <v>123</v>
+      </c>
+      <c r="D7" s="26" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="65" x14ac:dyDescent="0.35">
       <c r="A8" s="12" t="s">
-        <v>116</v>
+        <v>80</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>117</v>
-      </c>
-      <c r="C8" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="D8" s="13"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+        <v>81</v>
+      </c>
+      <c r="C8" s="25" t="s">
+        <v>123</v>
+      </c>
+      <c r="D8" s="26" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="65" x14ac:dyDescent="0.35">
       <c r="A9" s="12" t="s">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>119</v>
-      </c>
-      <c r="C9" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="D9" s="13"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+        <v>83</v>
+      </c>
+      <c r="C9" s="25" t="s">
+        <v>123</v>
+      </c>
+      <c r="D9" s="26" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="65" x14ac:dyDescent="0.35">
       <c r="A10" s="12" t="s">
-        <v>120</v>
+        <v>84</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="D10" s="13"/>
+        <v>85</v>
+      </c>
+      <c r="C10" s="25" t="s">
+        <v>123</v>
+      </c>
+      <c r="D10" s="26" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="12" spans="1:4" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A12" s="1" t="s">
-        <v>122</v>
+        <v>86</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" s="6" t="s">
-        <v>107</v>
+        <v>72</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>108</v>
+        <v>73</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="D13" s="11" t="s">
-        <v>123</v>
+        <v>74</v>
+      </c>
+      <c r="D13" s="27" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" s="12" t="s">
-        <v>111</v>
+        <v>76</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>124</v>
-      </c>
-      <c r="C14" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="D14" s="13"/>
+        <v>88</v>
+      </c>
+      <c r="C14" s="25" t="s">
+        <v>123</v>
+      </c>
+      <c r="D14" s="13">
+        <v>2</v>
+      </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" s="12" t="s">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>125</v>
-      </c>
-      <c r="C15" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="D15" s="13"/>
+        <v>89</v>
+      </c>
+      <c r="C15" s="25" t="s">
+        <v>123</v>
+      </c>
+      <c r="D15" s="13">
+        <v>2</v>
+      </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" s="12" t="s">
-        <v>116</v>
+        <v>80</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>126</v>
-      </c>
-      <c r="C16" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="D16" s="13"/>
+        <v>90</v>
+      </c>
+      <c r="C16" s="25" t="s">
+        <v>123</v>
+      </c>
+      <c r="D16" s="13">
+        <v>1</v>
+      </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" s="12" t="s">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>127</v>
-      </c>
-      <c r="C17" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="D17" s="13"/>
+        <v>91</v>
+      </c>
+      <c r="C17" s="25" t="s">
+        <v>123</v>
+      </c>
+      <c r="D17" s="28">
+        <v>1</v>
+      </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" s="12" t="s">
-        <v>120</v>
+        <v>84</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>128</v>
-      </c>
-      <c r="C18" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="D18" s="13"/>
+        <v>92</v>
+      </c>
+      <c r="C18" s="25" t="s">
+        <v>123</v>
+      </c>
+      <c r="D18" s="28">
+        <v>1</v>
+      </c>
     </row>
     <row r="20" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A20" s="14" t="s">
-        <v>129</v>
+        <v>93</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" s="15" t="s">
-        <v>130</v>
+        <v>94</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" s="15" t="s">
-        <v>131</v>
+        <v>95</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A25" s="1" t="s">
-        <v>132</v>
+        <v>96</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26" s="16" t="s">
-        <v>133</v>
+        <v>97</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A27" s="17" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>134</v>
+        <v>98</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>135</v>
+        <v>99</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A28" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="B28" s="7"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="7"/>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+        <v>37</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A29" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="B29" s="7"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="7"/>
+        <v>39</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>130</v>
+      </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30" s="9" t="s">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="B30" s="7"/>
       <c r="C30" s="7"/>
